--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/1000000/Output_9_12.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/1000000/Output_9_12.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63392.52171979594</v>
+        <v>52390.90740707647</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9858951.653791893</v>
+        <v>10412381.74029742</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22081763.57343303</v>
+        <v>22003224.81690028</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4145624.528972384</v>
+        <v>4142060.289825662</v>
       </c>
     </row>
     <row r="11">
@@ -8196,22 +8196,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K5" t="n">
-        <v>220.0898510449805</v>
+        <v>218.2111409464629</v>
       </c>
       <c r="L5" t="n">
-        <v>235.7664149699872</v>
+        <v>233.4357089658653</v>
       </c>
       <c r="M5" t="n">
-        <v>230.3462332272727</v>
+        <v>227.7528737187178</v>
       </c>
       <c r="N5" t="n">
-        <v>229.4130635965909</v>
+        <v>226.7777408199137</v>
       </c>
       <c r="O5" t="n">
-        <v>230.0982114216867</v>
+        <v>227.6097508526263</v>
       </c>
       <c r="P5" t="n">
-        <v>231.2329957552695</v>
+        <v>229.1091522321465</v>
       </c>
       <c r="Q5" t="n">
         <v>212.3149906599047</v>
@@ -8275,25 +8275,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K6" t="n">
-        <v>137.841438974359</v>
+        <v>136.5653954824675</v>
       </c>
       <c r="L6" t="n">
-        <v>138.5543797798742</v>
+        <v>136.8385818314783</v>
       </c>
       <c r="M6" t="n">
-        <v>142.1340339220183</v>
+        <v>140.1317786452013</v>
       </c>
       <c r="N6" t="n">
-        <v>131.3417120833333</v>
+        <v>129.2864630672354</v>
       </c>
       <c r="O6" t="n">
-        <v>142.5962444444444</v>
+        <v>140.7160931202018</v>
       </c>
       <c r="P6" t="n">
-        <v>133.9744074143302</v>
+        <v>132.4654202195568</v>
       </c>
       <c r="Q6" t="n">
-        <v>139.9817740860215</v>
+        <v>138.9730561082392</v>
       </c>
       <c r="R6" t="n">
         <v>45.52166981132082</v>
@@ -8357,16 +8357,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L7" t="n">
-        <v>134.8846762812383</v>
+        <v>133.8997196622861</v>
       </c>
       <c r="M7" t="n">
-        <v>138.9257839476051</v>
+        <v>137.8872852940284</v>
       </c>
       <c r="N7" t="n">
-        <v>127.6855444652332</v>
+        <v>126.6717389884799</v>
       </c>
       <c r="O7" t="n">
-        <v>138.4565384518428</v>
+        <v>137.5201250048898</v>
       </c>
       <c r="P7" t="n">
         <v>135.0065633140411</v>
@@ -8430,28 +8430,28 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>169.0966151720738</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K8" t="n">
-        <v>213.4420168741263</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L8" t="n">
-        <v>227.519188839334</v>
+        <v>86.82148686318186</v>
       </c>
       <c r="M8" t="n">
-        <v>221.1696050865692</v>
+        <v>64.61630209323863</v>
       </c>
       <c r="N8" t="n">
-        <v>220.0879480187015</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O8" t="n">
-        <v>221.2927692106315</v>
+        <v>71.0718992657024</v>
       </c>
       <c r="P8" t="n">
-        <v>223.7177545492394</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q8" t="n">
-        <v>212.3149906599047</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R8" t="n">
         <v>65.71641987298243</v>
@@ -8509,28 +8509,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J9" t="n">
-        <v>124.1958059119497</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K9" t="n">
-        <v>133.3261465215288</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L9" t="n">
-        <v>132.4830118553459</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M9" t="n">
-        <v>135.0490339220183</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N9" t="n">
-        <v>124.0691932154088</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>135.9433104821803</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P9" t="n">
-        <v>128.6348413765944</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q9" t="n">
-        <v>136.4124155954555</v>
+        <v>75.51914927829571</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8591,22 +8591,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K10" t="n">
-        <v>106.7437663446525</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L10" t="n">
-        <v>131.3993975927137</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M10" t="n">
-        <v>135.251046242687</v>
+        <v>72.56001021962938</v>
       </c>
       <c r="N10" t="n">
-        <v>124.0981838094955</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O10" t="n">
-        <v>135.1430302551215</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P10" t="n">
-        <v>134.892725360623</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q10" t="n">
         <v>65.34295837775146</v>
@@ -8667,28 +8667,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K11" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L11" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M11" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226639</v>
       </c>
       <c r="N11" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O11" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P11" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q11" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026311</v>
       </c>
       <c r="R11" t="n">
         <v>65.71641987298243</v>
@@ -8746,13 +8746,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J12" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979123</v>
       </c>
       <c r="K12" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043561</v>
       </c>
       <c r="L12" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -8764,10 +8764,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380177</v>
       </c>
       <c r="Q12" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8828,22 +8828,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K13" t="n">
-        <v>70.56047128528949</v>
+        <v>66.8579709251007</v>
       </c>
       <c r="L13" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M13" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N13" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O13" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P13" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703003</v>
       </c>
       <c r="Q13" t="n">
         <v>65.34295837775146</v>
@@ -8904,28 +8904,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K14" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L14" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M14" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N14" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O14" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P14" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q14" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R14" t="n">
         <v>65.71641987298243</v>
@@ -8983,13 +8983,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J15" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K15" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L15" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -9001,10 +9001,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q15" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9065,22 +9065,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K16" t="n">
-        <v>70.56047128528949</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L16" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M16" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N16" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O16" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P16" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q16" t="n">
         <v>65.34295837775146</v>
@@ -9141,28 +9141,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K17" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L17" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M17" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N17" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O17" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P17" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q17" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R17" t="n">
         <v>65.71641987298243</v>
@@ -9220,13 +9220,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J18" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K18" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L18" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -9238,10 +9238,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q18" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9302,22 +9302,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K19" t="n">
-        <v>70.56047128528949</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L19" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M19" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N19" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O19" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P19" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q19" t="n">
         <v>65.34295837775146</v>
@@ -9378,28 +9378,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K20" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L20" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M20" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N20" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O20" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P20" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q20" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R20" t="n">
         <v>65.71641987298243</v>
@@ -9457,13 +9457,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J21" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K21" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L21" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -9475,10 +9475,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q21" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9539,22 +9539,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K22" t="n">
-        <v>70.56047128528949</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L22" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M22" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N22" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O22" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P22" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q22" t="n">
         <v>65.34295837775146</v>
@@ -9615,28 +9615,28 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K23" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L23" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M23" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N23" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O23" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P23" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q23" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R23" t="n">
         <v>65.71641987298243</v>
@@ -9694,13 +9694,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J24" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K24" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L24" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -9712,10 +9712,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q24" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9776,22 +9776,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K25" t="n">
-        <v>70.56047128528949</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L25" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M25" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N25" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O25" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P25" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q25" t="n">
         <v>65.34295837775146</v>
@@ -9852,28 +9852,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K26" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L26" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M26" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N26" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O26" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P26" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q26" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R26" t="n">
         <v>65.71641987298243</v>
@@ -9931,13 +9931,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J27" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K27" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L27" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -9949,10 +9949,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q27" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10013,22 +10013,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K28" t="n">
-        <v>70.56047128528949</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L28" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M28" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N28" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O28" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P28" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q28" t="n">
         <v>65.34295837775146</v>
@@ -10089,28 +10089,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K29" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L29" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M29" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N29" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O29" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P29" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q29" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R29" t="n">
         <v>65.71641987298243</v>
@@ -10168,13 +10168,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J30" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K30" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L30" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -10186,10 +10186,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q30" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10250,22 +10250,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K31" t="n">
-        <v>70.56047128528949</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L31" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M31" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N31" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O31" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P31" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q31" t="n">
         <v>65.34295837775146</v>
@@ -10326,28 +10326,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K32" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L32" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M32" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N32" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O32" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P32" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q32" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R32" t="n">
         <v>65.71641987298243</v>
@@ -10405,13 +10405,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J33" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K33" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L33" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -10423,10 +10423,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q33" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10487,22 +10487,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K34" t="n">
-        <v>70.56047128528949</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L34" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M34" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N34" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O34" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P34" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q34" t="n">
         <v>65.34295837775146</v>
@@ -10563,28 +10563,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K35" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L35" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M35" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N35" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O35" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P35" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q35" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R35" t="n">
         <v>65.71641987298243</v>
@@ -10642,13 +10642,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J36" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K36" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L36" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -10660,10 +10660,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q36" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10724,22 +10724,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K37" t="n">
-        <v>70.56047128528949</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L37" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M37" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N37" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O37" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P37" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q37" t="n">
         <v>65.34295837775146</v>
@@ -10800,28 +10800,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K38" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L38" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M38" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N38" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O38" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P38" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q38" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R38" t="n">
         <v>65.71641987298243</v>
@@ -10879,13 +10879,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J39" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K39" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L39" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -10897,10 +10897,10 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q39" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10961,22 +10961,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K40" t="n">
-        <v>70.56047128528949</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L40" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M40" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N40" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O40" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P40" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q40" t="n">
         <v>65.34295837775146</v>
@@ -11037,28 +11037,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K41" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L41" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M41" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N41" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O41" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P41" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q41" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R41" t="n">
         <v>65.71641987298243</v>
@@ -11116,13 +11116,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J42" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K42" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L42" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -11134,10 +11134,10 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q42" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11198,22 +11198,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K43" t="n">
-        <v>70.56047128528949</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L43" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M43" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N43" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O43" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P43" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q43" t="n">
         <v>65.34295837775146</v>
@@ -11274,28 +11274,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K44" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L44" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M44" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N44" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O44" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P44" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q44" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R44" t="n">
         <v>65.71641987298243</v>
@@ -11353,13 +11353,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J45" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K45" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L45" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -11371,10 +11371,10 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q45" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -11435,22 +11435,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K46" t="n">
-        <v>70.56047128528949</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L46" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M46" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N46" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O46" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P46" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q46" t="n">
         <v>65.34295837775146</v>
@@ -22756,16 +22756,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G5" t="n">
-        <v>415.302737515135</v>
+        <v>415.2879682170718</v>
       </c>
       <c r="H5" t="n">
-        <v>339.4748021157671</v>
+        <v>339.3235460419765</v>
       </c>
       <c r="I5" t="n">
-        <v>210.4758895704059</v>
+        <v>209.9064962068211</v>
       </c>
       <c r="J5" t="n">
-        <v>11.94928935461252</v>
+        <v>10.69576364311372</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -22786,19 +22786,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.990699214544804</v>
+        <v>8.395781178313161</v>
       </c>
       <c r="R5" t="n">
-        <v>149.8691179411497</v>
+        <v>148.9413660216818</v>
       </c>
       <c r="S5" t="n">
-        <v>209.0200695862453</v>
+        <v>208.6835142066282</v>
       </c>
       <c r="T5" t="n">
-        <v>223.0958495641314</v>
+        <v>223.0311969618593</v>
       </c>
       <c r="U5" t="n">
-        <v>251.3456529078365</v>
+        <v>251.3444713639914</v>
       </c>
       <c r="V5" t="n">
         <v>327.7522584701349</v>
@@ -22835,16 +22835,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G6" t="n">
-        <v>137.3435171632106</v>
+        <v>137.3356148920818</v>
       </c>
       <c r="H6" t="n">
-        <v>112.2354442364965</v>
+        <v>112.1591249337519</v>
       </c>
       <c r="I6" t="n">
-        <v>89.39663285141508</v>
+        <v>89.12455904281175</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -22868,16 +22868,16 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>100.1578341526431</v>
+        <v>99.6672001609758</v>
       </c>
       <c r="S6" t="n">
-        <v>171.6831711038378</v>
+        <v>171.5363898835276</v>
       </c>
       <c r="T6" t="n">
-        <v>200.1647286948216</v>
+        <v>200.1328769967189</v>
       </c>
       <c r="U6" t="n">
-        <v>225.9413820809748</v>
+        <v>225.9408621947163</v>
       </c>
       <c r="V6" t="n">
         <v>232.8005871494253</v>
@@ -22914,19 +22914,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G7" t="n">
-        <v>167.9909793584588</v>
+        <v>167.9843543597988</v>
       </c>
       <c r="H7" t="n">
-        <v>162.2271725074396</v>
+        <v>162.1682702466266</v>
       </c>
       <c r="I7" t="n">
-        <v>155.4504749272583</v>
+        <v>155.2512431493756</v>
       </c>
       <c r="J7" t="n">
-        <v>93.35918011667277</v>
+        <v>92.89079271141465</v>
       </c>
       <c r="K7" t="n">
-        <v>22.26949182588285</v>
+        <v>21.49978743611831</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -22941,22 +22941,22 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.721440735106512</v>
+        <v>1.920177260816417</v>
       </c>
       <c r="Q7" t="n">
-        <v>86.16204325169439</v>
+        <v>85.60728995481479</v>
       </c>
       <c r="R7" t="n">
-        <v>177.2933913771695</v>
+        <v>176.9955073465141</v>
       </c>
       <c r="S7" t="n">
-        <v>224.0165980369723</v>
+        <v>223.9011423785076</v>
       </c>
       <c r="T7" t="n">
-        <v>227.9455894282815</v>
+        <v>227.9172826158254</v>
       </c>
       <c r="U7" t="n">
-        <v>286.3190293564909</v>
+        <v>286.3186679929276</v>
       </c>
       <c r="V7" t="n">
         <v>252.137643323828</v>
@@ -22993,16 +22993,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G8" t="n">
-        <v>415.2504762086024</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H8" t="n">
-        <v>338.9395810102395</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I8" t="n">
-        <v>208.4610855503054</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J8" t="n">
-        <v>7.513676289285883</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -23023,19 +23023,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.347066048715659</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>146.5862586446673</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S8" t="n">
-        <v>207.8291650636323</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T8" t="n">
-        <v>222.8670756947846</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U8" t="n">
-        <v>251.3414720033139</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V8" t="n">
         <v>327.7522584701349</v>
@@ -23072,13 +23072,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>137.3155548990597</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H9" t="n">
-        <v>111.9653876327229</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I9" t="n">
-        <v>88.43389700235848</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -23105,16 +23105,16 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>98.42172094509596</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S9" t="n">
-        <v>171.163784311385</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T9" t="n">
-        <v>200.0520211476518</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U9" t="n">
-        <v>225.9395424583333</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V9" t="n">
         <v>232.8005871494253</v>
@@ -23151,19 +23151,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.9675367355079</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H10" t="n">
-        <v>162.0187462779314</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I10" t="n">
-        <v>154.7454913207009</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J10" t="n">
-        <v>91.70178667404983</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K10" t="n">
-        <v>19.5458852685058</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -23181,19 +23181,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>84.19904325169439</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R10" t="n">
-        <v>176.239325803399</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S10" t="n">
-        <v>223.6080570533657</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T10" t="n">
-        <v>227.8454254938553</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U10" t="n">
-        <v>286.3177506679663</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V10" t="n">
         <v>252.137643323828</v>
@@ -23230,13 +23230,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H11" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I11" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,16 +23263,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296736</v>
       </c>
       <c r="S11" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167796</v>
       </c>
       <c r="T11" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U11" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23309,13 +23309,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H12" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I12" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,16 +23342,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>62.89817377528463</v>
+        <v>60.53808260908391</v>
       </c>
       <c r="S12" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T12" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U12" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23388,16 +23388,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H13" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I13" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J13" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23418,19 +23418,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R13" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S13" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T13" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U13" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23467,13 +23467,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H14" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I14" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,16 +23500,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S14" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T14" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U14" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,13 +23546,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H15" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I15" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>62.89817377528463</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S15" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T15" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U15" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,16 +23625,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H16" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I16" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J16" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23655,19 +23655,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R16" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S16" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T16" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U16" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V16" t="n">
         <v>252.137643323828</v>
@@ -23704,13 +23704,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H17" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I17" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,16 +23737,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S17" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T17" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U17" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,13 +23783,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H18" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I18" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>62.89817377528463</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S18" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T18" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23862,16 +23862,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H19" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I19" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J19" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -23892,19 +23892,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R19" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S19" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T19" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U19" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23941,13 +23941,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H20" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I20" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,16 +23974,16 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S20" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T20" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U20" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
@@ -24020,13 +24020,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H21" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I21" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -24053,16 +24053,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>62.89817377528463</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S21" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T21" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24099,16 +24099,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H22" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I22" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J22" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -24129,19 +24129,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R22" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S22" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T22" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U22" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24178,13 +24178,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H23" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I23" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,16 +24211,16 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S23" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T23" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U23" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24257,13 +24257,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H24" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I24" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -24290,16 +24290,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>62.89817377528463</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S24" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T24" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24336,16 +24336,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H25" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I25" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J25" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -24366,19 +24366,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R25" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S25" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T25" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U25" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24415,13 +24415,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H26" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I26" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,16 +24448,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S26" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T26" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U26" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24494,13 +24494,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H27" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I27" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,16 +24527,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>62.89817377528463</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S27" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T27" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24573,16 +24573,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H28" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I28" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J28" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24603,19 +24603,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R28" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S28" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T28" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U28" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24652,13 +24652,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H29" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I29" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,16 +24685,16 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S29" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T29" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U29" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24731,13 +24731,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H30" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I30" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -24764,16 +24764,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>62.89817377528463</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S30" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T30" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24810,16 +24810,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H31" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I31" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J31" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -24840,19 +24840,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R31" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S31" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T31" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U31" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24889,13 +24889,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H32" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I32" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,16 +24922,16 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S32" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T32" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U32" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24968,13 +24968,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H33" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I33" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -25001,16 +25001,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>62.89817377528463</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S33" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T33" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25047,16 +25047,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H34" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I34" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J34" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -25077,19 +25077,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R34" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S34" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T34" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U34" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25126,13 +25126,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H35" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I35" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,16 +25159,16 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S35" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T35" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U35" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25205,13 +25205,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H36" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I36" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -25238,16 +25238,16 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>62.89817377528463</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S36" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T36" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -25284,16 +25284,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H37" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I37" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J37" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -25314,19 +25314,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R37" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S37" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T37" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U37" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25363,13 +25363,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H38" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I38" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,16 +25396,16 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S38" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T38" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U38" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25442,13 +25442,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H39" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I39" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -25475,16 +25475,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>62.89817377528463</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S39" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T39" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25521,16 +25521,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H40" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I40" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J40" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -25551,19 +25551,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R40" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S40" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T40" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U40" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25600,13 +25600,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H41" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I41" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,16 +25633,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S41" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T41" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U41" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25679,13 +25679,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H42" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I42" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25712,16 +25712,16 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>62.89817377528463</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S42" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T42" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
@@ -25758,16 +25758,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H43" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I43" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J43" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -25788,19 +25788,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R43" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S43" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T43" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U43" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25837,13 +25837,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H44" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I44" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25870,16 +25870,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S44" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T44" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U44" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,13 +25916,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H45" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I45" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25949,16 +25949,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>62.89817377528463</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S45" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T45" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U45" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,16 +25995,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H46" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I46" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J46" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -26025,19 +26025,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R46" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S46" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T46" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U46" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>360149.8085303454</v>
+        <v>360558.5304388088</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>361456.8995456908</v>
+        <v>358557.8067513343</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64504.44331886783</v>
+        <v>64504.44331886782</v>
       </c>
       <c r="C2" t="n">
-        <v>64504.44331886782</v>
+        <v>64668.10444303643</v>
       </c>
       <c r="D2" t="n">
-        <v>65058.63286563388</v>
+        <v>70000.02111109273</v>
       </c>
       <c r="E2" t="n">
-        <v>70900.73467282811</v>
+        <v>71260.70145735366</v>
       </c>
       <c r="F2" t="n">
-        <v>70900.73467282811</v>
+        <v>71260.70145735363</v>
       </c>
       <c r="G2" t="n">
-        <v>70900.73467282811</v>
+        <v>71260.70145735364</v>
       </c>
       <c r="H2" t="n">
-        <v>70900.73467282808</v>
+        <v>71260.70145735364</v>
       </c>
       <c r="I2" t="n">
-        <v>70900.73467282808</v>
+        <v>71260.70145735363</v>
       </c>
       <c r="J2" t="n">
-        <v>70900.73467282808</v>
+        <v>71260.70145735364</v>
       </c>
       <c r="K2" t="n">
-        <v>70900.73467282813</v>
+        <v>71260.70145735361</v>
       </c>
       <c r="L2" t="n">
-        <v>70900.7346728281</v>
+        <v>71260.70145735363</v>
       </c>
       <c r="M2" t="n">
-        <v>70900.73467282808</v>
+        <v>71260.70145735364</v>
       </c>
       <c r="N2" t="n">
-        <v>70900.73467282807</v>
+        <v>71260.70145735364</v>
       </c>
       <c r="O2" t="n">
-        <v>70900.73467282808</v>
+        <v>71260.70145735364</v>
       </c>
       <c r="P2" t="n">
-        <v>70900.73467282811</v>
+        <v>71260.70145735363</v>
       </c>
     </row>
     <row r="3">
@@ -26316,13 +26316,13 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3345.426898312242</v>
       </c>
       <c r="D3" t="n">
-        <v>11133.382</v>
+        <v>197922.563955782</v>
       </c>
       <c r="E3" t="n">
-        <v>213705.198</v>
+        <v>49724.46205680795</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48378.33248915087</v>
+        <v>50994.57005901547</v>
       </c>
       <c r="C4" t="n">
-        <v>48378.33248915088</v>
+        <v>50591.58854086108</v>
       </c>
       <c r="D4" t="n">
-        <v>47006.84069512705</v>
+        <v>21318.07919427381</v>
       </c>
       <c r="E4" t="n">
-        <v>15153.32488392675</v>
+        <v>13983.75656052792</v>
       </c>
       <c r="F4" t="n">
-        <v>15153.32488392675</v>
+        <v>13983.75656052792</v>
       </c>
       <c r="G4" t="n">
-        <v>15153.32488392675</v>
+        <v>13983.75656052792</v>
       </c>
       <c r="H4" t="n">
-        <v>15153.32488392675</v>
+        <v>13983.75656052792</v>
       </c>
       <c r="I4" t="n">
-        <v>15153.32488392675</v>
+        <v>13983.75656052792</v>
       </c>
       <c r="J4" t="n">
-        <v>15153.32488392675</v>
+        <v>13983.75656052792</v>
       </c>
       <c r="K4" t="n">
-        <v>15153.32488392675</v>
+        <v>13983.75656052792</v>
       </c>
       <c r="L4" t="n">
-        <v>15153.32488392675</v>
+        <v>13983.75656052792</v>
       </c>
       <c r="M4" t="n">
-        <v>15153.32488392675</v>
+        <v>13983.75656052792</v>
       </c>
       <c r="N4" t="n">
-        <v>15153.32488392675</v>
+        <v>13983.75656052792</v>
       </c>
       <c r="O4" t="n">
-        <v>15153.32488392675</v>
+        <v>13983.75656052792</v>
       </c>
       <c r="P4" t="n">
-        <v>15153.32488392675</v>
+        <v>13983.75656052792</v>
       </c>
     </row>
     <row r="5">
@@ -26420,46 +26420,46 @@
         <v>33627.6</v>
       </c>
       <c r="C5" t="n">
-        <v>33627.6</v>
+        <v>33707.69021107268</v>
       </c>
       <c r="D5" t="n">
-        <v>33911</v>
+        <v>38745.80483114667</v>
       </c>
       <c r="E5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="F5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="G5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="H5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="I5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="J5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="K5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="L5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="M5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="N5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="O5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="P5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-17501.48917028304</v>
+        <v>-20117.72674014765</v>
       </c>
       <c r="C6" t="n">
-        <v>-17501.48917028306</v>
+        <v>-22976.60120720958</v>
       </c>
       <c r="D6" t="n">
-        <v>-26992.58982949317</v>
+        <v>-187986.4268701097</v>
       </c>
       <c r="E6" t="n">
-        <v>-164039.9882110987</v>
+        <v>1085.025799409099</v>
       </c>
       <c r="F6" t="n">
-        <v>49665.20978890137</v>
+        <v>50809.48785621702</v>
       </c>
       <c r="G6" t="n">
-        <v>49665.20978890137</v>
+        <v>50809.48785621703</v>
       </c>
       <c r="H6" t="n">
-        <v>49665.20978890134</v>
+        <v>50809.48785621703</v>
       </c>
       <c r="I6" t="n">
-        <v>49665.20978890134</v>
+        <v>50809.48785621702</v>
       </c>
       <c r="J6" t="n">
-        <v>49665.20978890134</v>
+        <v>50809.48785621703</v>
       </c>
       <c r="K6" t="n">
-        <v>49665.20978890138</v>
+        <v>50809.48785621701</v>
       </c>
       <c r="L6" t="n">
-        <v>49665.20978890135</v>
+        <v>50809.48785621702</v>
       </c>
       <c r="M6" t="n">
-        <v>49665.20978890134</v>
+        <v>50809.48785621703</v>
       </c>
       <c r="N6" t="n">
-        <v>49665.20978890132</v>
+        <v>50809.48785621703</v>
       </c>
       <c r="O6" t="n">
-        <v>49665.20978890134</v>
+        <v>50809.48785621703</v>
       </c>
       <c r="P6" t="n">
-        <v>49665.20978890137</v>
+        <v>50809.48785621702</v>
       </c>
     </row>
   </sheetData>
@@ -26678,46 +26678,46 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3.673862893242319</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="E3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="F3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="G3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="H3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="I3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="J3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="K3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="L3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="M3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="N3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="O3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="P3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
     </row>
     <row r="4">
@@ -26895,13 +26895,13 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3.673862893242319</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>231.1061752327519</v>
       </c>
       <c r="E3" t="n">
-        <v>266</v>
+        <v>61.89230318633108</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -31196,49 +31196,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.01476929806328569</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.1512560737906247</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.5693933635848223</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1.253525711498795</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1.878710098517679</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.330706004121959</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.593359508554916</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.635322776677227</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.488460569060429</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.123843523123063</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.594918036231644</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.9277519194678707</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.3365553796171231</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.06465260227203316</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.001181543845062855</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31275,49 +31275,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.007902271128860838</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.07631930274452442</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.2720738086033228</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.276043491891533</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.715797948395859</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.002255276817064</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.05524901609789</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.880151324242605</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.508987194773435</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.008717977782306</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.4906339916673424</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.1467812203102001</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.03185169810273293</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.000519886258477687</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31354,49 +31354,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.006624998659945164</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.05890226081296705</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.1992317778827147</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.4683874052581232</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.7697043897645381</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.9849566189522113</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.038498653576677</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.013805476753246</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.936413446952977</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.8012634742900949</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>0.5547532968795902</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.2978840306553525</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.1154556584646807</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.02830681245612933</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.0003613635632697367</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31433,49 +31433,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05226130653266328</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5352211055276379</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I8" t="n">
-        <v>2.014804020100503</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J8" t="n">
-        <v>4.435613065326634</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K8" t="n">
-        <v>6.647834170854272</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L8" t="n">
-        <v>8.247226130653267</v>
+        <v>148.9449281068054</v>
       </c>
       <c r="M8" t="n">
-        <v>9.176628140703517</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N8" t="n">
-        <v>9.325115577889449</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O8" t="n">
-        <v>8.805442211055276</v>
+        <v>159.0263121559843</v>
       </c>
       <c r="P8" t="n">
-        <v>7.515241206030151</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.643633165829145</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R8" t="n">
-        <v>3.282859296482413</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S8" t="n">
-        <v>1.190904522613066</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2287738693467336</v>
+        <v>4.131656751342871</v>
       </c>
       <c r="U8" t="n">
-        <v>0.004180904522613061</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31512,49 +31512,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0279622641509434</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H9" t="n">
-        <v>0.270056603773585</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9627358490566039</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J9" t="n">
-        <v>2.641820754716981</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K9" t="n">
-        <v>4.515292452830189</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L9" t="n">
-        <v>6.071367924528302</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M9" t="n">
-        <v>7.084999999999999</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N9" t="n">
-        <v>7.272518867924529</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
-        <v>6.652933962264151</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P9" t="n">
-        <v>5.33956603773585</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.569358490566038</v>
+        <v>64.4626248077258</v>
       </c>
       <c r="R9" t="n">
-        <v>1.736113207547171</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5193867924528298</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1127075471698113</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001839622641509435</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31591,49 +31591,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02344262295081967</v>
+        <v>0.423373839243596</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2084262295081968</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7049836065573772</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J10" t="n">
-        <v>1.657393442622951</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K10" t="n">
-        <v>2.723606557377048</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L10" t="n">
-        <v>3.48527868852459</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M10" t="n">
-        <v>3.674737704918032</v>
+        <v>66.36577372797568</v>
       </c>
       <c r="N10" t="n">
-        <v>3.587360655737707</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O10" t="n">
-        <v>3.313508196721312</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P10" t="n">
-        <v>2.835278688524589</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.963</v>
+        <v>35.45178575702513</v>
       </c>
       <c r="R10" t="n">
-        <v>1.054065573770491</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4085409836065572</v>
+        <v>7.378251362090667</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1001639344262295</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U10" t="n">
-        <v>0.001278688524590165</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H11" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I11" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605395</v>
       </c>
       <c r="J11" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K11" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L11" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M11" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350063</v>
       </c>
       <c r="N11" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O11" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P11" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q11" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R11" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818232</v>
       </c>
       <c r="S11" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946578</v>
       </c>
       <c r="T11" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782727</v>
       </c>
       <c r="U11" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,22 +31749,22 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.638125413388775</v>
       </c>
       <c r="H12" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I12" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J12" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K12" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L12" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M12" t="n">
         <v>142.1340339220183</v>
@@ -31776,22 +31776,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q12" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R12" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S12" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T12" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U12" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H13" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I13" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J13" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K13" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543468</v>
       </c>
       <c r="L13" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M13" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N13" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O13" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P13" t="n">
-        <v>60.84944262295079</v>
+        <v>64.70375129211759</v>
       </c>
       <c r="Q13" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R13" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S13" t="n">
-        <v>8.767918032786881</v>
+        <v>9.3232930868152</v>
       </c>
       <c r="T13" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,49 +31907,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H14" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I14" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J14" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K14" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L14" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M14" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N14" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O14" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P14" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q14" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R14" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S14" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T14" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U14" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,22 +31986,22 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H15" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I15" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J15" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K15" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L15" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M15" t="n">
         <v>142.1340339220183</v>
@@ -32013,22 +32013,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q15" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R15" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S15" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T15" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U15" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H16" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I16" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J16" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K16" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L16" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M16" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N16" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O16" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P16" t="n">
-        <v>60.84944262295079</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q16" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R16" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S16" t="n">
-        <v>8.767918032786881</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T16" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,49 +32144,49 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H17" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I17" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J17" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K17" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L17" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M17" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N17" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O17" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P17" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q17" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R17" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S17" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T17" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U17" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,22 +32223,22 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H18" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I18" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J18" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K18" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L18" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M18" t="n">
         <v>142.1340339220183</v>
@@ -32250,22 +32250,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P18" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q18" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R18" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S18" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T18" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U18" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H19" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I19" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J19" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K19" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L19" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M19" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N19" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O19" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P19" t="n">
-        <v>60.84944262295079</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q19" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R19" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S19" t="n">
-        <v>8.767918032786881</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T19" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H20" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I20" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J20" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K20" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L20" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M20" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N20" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O20" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P20" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q20" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R20" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S20" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T20" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U20" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,22 +32460,22 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H21" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I21" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J21" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K21" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L21" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M21" t="n">
         <v>142.1340339220183</v>
@@ -32487,22 +32487,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P21" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q21" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R21" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S21" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T21" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U21" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H22" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I22" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J22" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K22" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L22" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M22" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N22" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O22" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P22" t="n">
-        <v>60.84944262295079</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q22" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R22" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S22" t="n">
-        <v>8.767918032786881</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T22" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,49 +32618,49 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H23" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I23" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J23" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K23" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L23" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M23" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N23" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O23" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P23" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q23" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R23" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S23" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T23" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U23" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,22 +32697,22 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H24" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I24" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J24" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K24" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L24" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M24" t="n">
         <v>142.1340339220183</v>
@@ -32724,22 +32724,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q24" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R24" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S24" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T24" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U24" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H25" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I25" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J25" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K25" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L25" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M25" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N25" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O25" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P25" t="n">
-        <v>60.84944262295079</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q25" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R25" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S25" t="n">
-        <v>8.767918032786881</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T25" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H26" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I26" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J26" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K26" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L26" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M26" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N26" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O26" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P26" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q26" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R26" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S26" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T26" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U26" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,22 +32934,22 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H27" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I27" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J27" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K27" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L27" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M27" t="n">
         <v>142.1340339220183</v>
@@ -32961,22 +32961,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P27" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q27" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R27" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S27" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T27" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U27" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H28" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I28" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J28" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K28" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L28" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M28" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N28" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O28" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P28" t="n">
-        <v>60.84944262295079</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q28" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R28" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S28" t="n">
-        <v>8.767918032786881</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T28" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U28" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H29" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I29" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J29" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K29" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L29" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M29" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N29" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O29" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P29" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q29" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R29" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S29" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T29" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U29" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,22 +33171,22 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H30" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I30" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J30" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K30" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L30" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M30" t="n">
         <v>142.1340339220183</v>
@@ -33198,22 +33198,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P30" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q30" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R30" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S30" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T30" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U30" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H31" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I31" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J31" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K31" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L31" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M31" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N31" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O31" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P31" t="n">
-        <v>60.84944262295079</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q31" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R31" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S31" t="n">
-        <v>8.767918032786881</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T31" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U31" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,49 +33329,49 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H32" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I32" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J32" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K32" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L32" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M32" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N32" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O32" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P32" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q32" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R32" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S32" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T32" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U32" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,22 +33408,22 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H33" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I33" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J33" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K33" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L33" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M33" t="n">
         <v>142.1340339220183</v>
@@ -33435,22 +33435,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P33" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q33" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R33" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S33" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T33" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U33" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H34" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I34" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J34" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K34" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L34" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M34" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N34" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O34" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P34" t="n">
-        <v>60.84944262295079</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q34" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R34" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S34" t="n">
-        <v>8.767918032786881</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T34" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U34" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H35" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I35" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J35" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K35" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L35" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M35" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N35" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O35" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P35" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q35" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R35" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S35" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T35" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U35" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,22 +33645,22 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H36" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I36" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J36" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K36" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L36" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M36" t="n">
         <v>142.1340339220183</v>
@@ -33672,22 +33672,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q36" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R36" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S36" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T36" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U36" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H37" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I37" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J37" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K37" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L37" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M37" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N37" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O37" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P37" t="n">
-        <v>60.84944262295079</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q37" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R37" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S37" t="n">
-        <v>8.767918032786881</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T37" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U37" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H38" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I38" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J38" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K38" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L38" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M38" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N38" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O38" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P38" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q38" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R38" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S38" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T38" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U38" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,22 +33882,22 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H39" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I39" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J39" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K39" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L39" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M39" t="n">
         <v>142.1340339220183</v>
@@ -33909,22 +33909,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q39" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R39" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S39" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T39" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U39" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H40" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I40" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J40" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K40" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L40" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M40" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N40" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O40" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P40" t="n">
-        <v>60.84944262295079</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q40" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R40" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S40" t="n">
-        <v>8.767918032786881</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T40" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U40" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H41" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I41" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J41" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K41" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L41" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M41" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N41" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O41" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P41" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q41" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R41" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S41" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T41" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U41" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,22 +34119,22 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H42" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I42" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J42" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K42" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L42" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M42" t="n">
         <v>142.1340339220183</v>
@@ -34146,22 +34146,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q42" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R42" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S42" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T42" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U42" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H43" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I43" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J43" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K43" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L43" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M43" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N43" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O43" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P43" t="n">
-        <v>60.84944262295079</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q43" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R43" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S43" t="n">
-        <v>8.767918032786881</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T43" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U43" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H44" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I44" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J44" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K44" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L44" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M44" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N44" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O44" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P44" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q44" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R44" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S44" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T44" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U44" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,22 +34356,22 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H45" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I45" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J45" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K45" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L45" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M45" t="n">
         <v>142.1340339220183</v>
@@ -34383,22 +34383,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P45" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q45" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R45" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S45" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T45" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U45" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H46" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I46" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J46" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K46" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L46" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M46" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N46" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O46" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P46" t="n">
-        <v>60.84944262295079</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q46" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R46" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S46" t="n">
-        <v>8.767918032786881</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T46" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U46" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
